--- a/src/test/resources/testData/BookingData.xlsx
+++ b/src/test/resources/testData/BookingData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2481483\IdeaProjects\Cognizant-Hackathon-Project\src\test\resources\testData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2481698\IdeaProjects\Cognizant-Hackathon-Project\src\test\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06212E96-0162-42B3-8C9D-A610A1D4F2B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC82FC2-581A-4D47-B1E0-6A6AC25B2BCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{963490A1-FD91-4158-9049-E2048162DBA5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
   <si>
     <t>City</t>
   </si>
@@ -75,6 +75,15 @@
   </si>
   <si>
     <t>XYZ</t>
+  </si>
+  <si>
+    <t>july</t>
+  </si>
+  <si>
+    <t>September</t>
+  </si>
+  <si>
+    <t>May</t>
   </si>
 </sst>
 </file>
@@ -464,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60143162-2827-47D6-BB51-80321F346896}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.26953125" customWidth="1"/>
@@ -559,15 +568,69 @@
         <v>2026</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="C4" s="1"/>
-      <c r="F4" s="1"/>
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4">
+        <v>2026</v>
+      </c>
+      <c r="E4">
+        <v>10</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4">
+        <v>2026</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>30</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5">
+        <v>2026</v>
+      </c>
+      <c r="E5">
+        <v>30</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <v>2026</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5" t="s">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
